--- a/تسعير جرد اخر شهر ٩ سنة ٢٠٢٦.xlsx
+++ b/تسعير جرد اخر شهر ٩ سنة ٢٠٢٦.xlsx
@@ -1801,7 +1801,7 @@
         <f>B8+C8</f>
       </c>
       <c r="H8" s="3">
-        <v>30</v>
+        <v>31.8123</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="1"/>
@@ -1814,7 +1814,7 @@
         <v>111</v>
       </c>
       <c r="L8" s="3">
-        <v>267.4006</v>
+        <v>269.1093</v>
       </c>
       <c r="M8" s="4">
         <f>K8*L8</f>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>86.0569</v>
+        <v>86.6264</v>
       </c>
       <c r="M9" s="4">
         <f>K9*L9</f>
@@ -1900,7 +1900,7 @@
         <v>101</v>
       </c>
       <c r="L10" s="3">
-        <v>75.1155</v>
+        <v>75.5712</v>
       </c>
       <c r="M10" s="4">
         <f>K10*L10</f>
@@ -1943,7 +1943,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="3">
-        <v>34.7899</v>
+        <v>34.9893</v>
       </c>
       <c r="M11" s="4">
         <f>K11*L11</f>
@@ -1973,7 +1973,7 @@
         <v>370</v>
       </c>
       <c r="H12" s="3">
-        <v>60</v>
+        <v>57.9003</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
@@ -1986,7 +1986,7 @@
         <v>23</v>
       </c>
       <c r="L12" s="3">
-        <v>71.9075</v>
+        <v>72.0511</v>
       </c>
       <c r="M12" s="4">
         <f>K12*L12</f>
@@ -2029,7 +2029,7 @@
         <v>34</v>
       </c>
       <c r="L13" s="3">
-        <v>33.6189</v>
+        <v>33.6817</v>
       </c>
       <c r="M13" s="4">
         <f>K13*L13</f>
@@ -2072,7 +2072,7 @@
         <v>18</v>
       </c>
       <c r="L14" s="3">
-        <v>123.9533</v>
+        <v>124.4455</v>
       </c>
       <c r="M14" s="4">
         <f>K14*L14</f>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>86.4478</v>
+        <v>86.8087</v>
       </c>
       <c r="M15" s="4">
         <f>K15*L15</f>
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>62.8711</v>
+        <v>63.1336</v>
       </c>
       <c r="M16" s="4">
         <f>K16*L16</f>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>53.1433</v>
+        <v>53.3402</v>
       </c>
       <c r="M17" s="4">
         <f>K17*L17</f>
@@ -2242,7 +2242,7 @@
         <v>121</v>
       </c>
       <c r="L18" s="3">
-        <v>36.4255</v>
+        <v>36.5568</v>
       </c>
       <c r="M18" s="4">
         <f>K18*L18</f>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>172.1137</v>
+        <v>173.2529</v>
       </c>
       <c r="M24" s="4">
         <f>K24*L24</f>
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="3">
-        <v>100.4866</v>
+        <v>100.8804</v>
       </c>
       <c r="M28" s="4">
         <f>K28*L28</f>
@@ -2718,7 +2718,7 @@
         <v>33</v>
       </c>
       <c r="L30" s="3">
-        <v>84.1889</v>
+        <v>84.517</v>
       </c>
       <c r="M30" s="4">
         <f>K30*L30</f>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>86.0569</v>
+        <v>86.6264</v>
       </c>
       <c r="M32" s="4">
         <f>K32*L32</f>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>415.9846</v>
+        <v>416.8821</v>
       </c>
       <c r="M33" s="4">
         <f>K33*L33</f>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>83.1969</v>
+        <v>83.3764</v>
       </c>
       <c r="M34" s="4">
         <f>K34*L34</f>
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>129.0853</v>
+        <v>129.9397</v>
       </c>
       <c r="M36" s="4">
         <f>K36*L36</f>
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="3">
-        <v>267.4006</v>
+        <v>269.1093</v>
       </c>
       <c r="M37" s="4">
         <f>K37*L37</f>
@@ -3091,7 +3091,7 @@
         <v>126</v>
       </c>
       <c r="L39" s="3">
-        <v>23.3497</v>
+        <v>23.9829</v>
       </c>
       <c r="M39" s="4">
         <f>K39*L39</f>
@@ -3134,7 +3134,7 @@
         <v>875</v>
       </c>
       <c r="L40" s="3">
-        <v>12.0699</v>
+        <v>12.3413</v>
       </c>
       <c r="M40" s="4">
         <f>K40*L40</f>
@@ -3177,7 +3177,7 @@
         <v>1633</v>
       </c>
       <c r="L41" s="3">
-        <v>25.9289</v>
+        <v>26.4849</v>
       </c>
       <c r="M41" s="4">
         <f>K41*L41</f>
@@ -3220,7 +3220,7 @@
         <v>1513</v>
       </c>
       <c r="L42" s="3">
-        <v>13.8639</v>
+        <v>14.1072</v>
       </c>
       <c r="M42" s="4">
         <f>K42*L42</f>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
-        <v>20.5086</v>
+        <v>21.146</v>
       </c>
       <c r="M43" s="4">
         <f>K43*L43</f>
@@ -3306,7 +3306,7 @@
         <v>1187</v>
       </c>
       <c r="L44" s="3">
-        <v>29.7022</v>
+        <v>30.4192</v>
       </c>
       <c r="M44" s="4">
         <f>K44*L44</f>
@@ -3349,7 +3349,7 @@
         <v>1183</v>
       </c>
       <c r="L45" s="3">
-        <v>8.9725</v>
+        <v>9.2514</v>
       </c>
       <c r="M45" s="4">
         <f>K45*L45</f>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>74.3987</v>
+        <v>77.1125</v>
       </c>
       <c r="M46" s="4">
         <f>K46*L46</f>
@@ -3435,7 +3435,7 @@
         <v>15</v>
       </c>
       <c r="L47" s="3">
-        <v>140.0579</v>
+        <v>144.5808</v>
       </c>
       <c r="M47" s="4">
         <f>K47*L47</f>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="3">
-        <v>140.0579</v>
+        <v>144.5808</v>
       </c>
       <c r="M51" s="4">
         <f>K51*L51</f>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>4.9599</v>
+        <v>5.1408</v>
       </c>
       <c r="M52" s="4">
         <f>K52*L52</f>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="3">
-        <v>7.6907</v>
+        <v>7.9297</v>
       </c>
       <c r="M53" s="4">
         <f>K53*L53</f>
@@ -3732,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="L54" s="3">
-        <v>4.9622</v>
+        <v>5.1012</v>
       </c>
       <c r="M54" s="4">
         <f>K54*L54</f>
@@ -3857,7 +3857,7 @@
         <v>370</v>
       </c>
       <c r="L57" s="3">
-        <v>31.5111</v>
+        <v>32.2062</v>
       </c>
       <c r="M57" s="4">
         <f>K57*L57</f>
@@ -3900,7 +3900,7 @@
         <v>541</v>
       </c>
       <c r="L58" s="3">
-        <v>15.4245</v>
+        <v>15.7025</v>
       </c>
       <c r="M58" s="4">
         <f>K58*L58</f>
@@ -3943,7 +3943,7 @@
         <v>1507</v>
       </c>
       <c r="L59" s="3">
-        <v>36.9991</v>
+        <v>37.7586</v>
       </c>
       <c r="M59" s="4">
         <f>K59*L59</f>
@@ -3986,7 +3986,7 @@
         <v>541</v>
       </c>
       <c r="L60" s="3">
-        <v>17.0885</v>
+        <v>17.3839</v>
       </c>
       <c r="M60" s="4">
         <f>K60*L60</f>
@@ -4029,7 +4029,7 @@
         <v>19</v>
       </c>
       <c r="L61" s="3">
-        <v>24.8056</v>
+        <v>25.9069</v>
       </c>
       <c r="M61" s="4">
         <f>K61*L61</f>
@@ -4072,7 +4072,7 @@
         <v>73</v>
       </c>
       <c r="L62" s="3">
-        <v>12.7452</v>
+        <v>13.2173</v>
       </c>
       <c r="M62" s="4">
         <f>K62*L62</f>
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="3">
-        <v>139.7541</v>
+        <v>147.6209</v>
       </c>
       <c r="M66" s="4">
         <f>K66*L66</f>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
-        <v>166.3938</v>
+        <v>166.7529</v>
       </c>
       <c r="M96" s="4">
         <f>K96*L96</f>
@@ -5572,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
-        <v>138.3157</v>
+        <v>141.7908</v>
       </c>
       <c r="M100" s="4">
         <f>K100*L100</f>
